--- a/utils/monday_sprint_sprint_2023-22.xlsx
+++ b/utils/monday_sprint_sprint_2023-22.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="158">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>17810</t>
+    <t>3710982740</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>26/12/2022</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>04/11/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>22560</t>
+    <t>5366184998</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -123,13 +123,16 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>22656</t>
+    <t>5366167891</t>
   </si>
   <si>
     <t>Relatório de Movimentação x Coleta</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>30/10/2023</t>
+  </si>
+  <si>
+    <t>5319552933</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -147,61 +150,73 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>22839</t>
+    <t>5365867709</t>
   </si>
   <si>
     <t>Follow-Up de compras</t>
   </si>
   <si>
-    <t>22784</t>
+    <t>22/10/2023</t>
+  </si>
+  <si>
+    <t>5365945246</t>
   </si>
   <si>
     <t>CRÉDITO PIS E COFINS CONSIGNADO</t>
   </si>
   <si>
-    <t>22793</t>
+    <t>5365932519</t>
   </si>
   <si>
     <t>Inventário BOX</t>
   </si>
   <si>
-    <t>22781</t>
+    <t>24/10/2023</t>
+  </si>
+  <si>
+    <t>5365967572</t>
   </si>
   <si>
     <t>Ticket - Separação Sequência de Amostra em SPS por Modelo (Alt+I)</t>
   </si>
   <si>
-    <t>22752</t>
+    <t>5366011291</t>
   </si>
   <si>
     <t>Sites Sistemas</t>
   </si>
   <si>
-    <t>22731</t>
+    <t>29/10/2023</t>
+  </si>
+  <si>
+    <t>5366025742</t>
   </si>
   <si>
     <t>Entrada Dep de pçs Estornadas</t>
   </si>
   <si>
-    <t>22718</t>
+    <t>01/11/2023</t>
+  </si>
+  <si>
+    <t>5366060720</t>
   </si>
   <si>
     <t>Tipo de embalagem no recebimento</t>
   </si>
   <si>
-    <t>22699</t>
+    <t>5366093507</t>
   </si>
   <si>
     <t>Inclusão de botão imprimir OS</t>
   </si>
   <si>
-    <t>22696</t>
+    <t>5366115724</t>
   </si>
   <si>
     <t>Tela espelho - sistema desmoldagem</t>
   </si>
   <si>
-    <t>23067</t>
+    <t>5435574802</t>
   </si>
   <si>
     <t>e-mail comunicado Compras</t>
@@ -210,7 +225,7 @@
     <t>Não definida</t>
   </si>
   <si>
-    <t>01/11/2023</t>
+    <t>31/10/2023</t>
   </si>
   <si>
     <t>Semana 1</t>
@@ -225,7 +240,7 @@
     <t>Fazer relatório de sequencias com setor zero na usinagem</t>
   </si>
   <si>
-    <t>22015</t>
+    <t>5123020151</t>
   </si>
   <si>
     <t>Análise</t>
@@ -240,7 +255,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>22557</t>
+    <t>5309015240</t>
   </si>
   <si>
     <t>Ao selecionar arquivo para importação do checklist</t>
@@ -249,13 +264,22 @@
     <t>10/10/2023</t>
   </si>
   <si>
+    <t>5309056874</t>
+  </si>
+  <si>
     <t>Permitir filtrar apenas as cotas reprovadas</t>
   </si>
   <si>
+    <t>5309060618</t>
+  </si>
+  <si>
     <t>Controlar e finalizar o PDI após todas as cotas preenchidas</t>
   </si>
   <si>
-    <t>22014</t>
+    <t>02/11/2023</t>
+  </si>
+  <si>
+    <t>5312699731</t>
   </si>
   <si>
     <t>Receber itens do processo</t>
@@ -264,19 +288,34 @@
     <t>11/10/2023</t>
   </si>
   <si>
+    <t>25/10/2023</t>
+  </si>
+  <si>
+    <t>5312700693</t>
+  </si>
+  <si>
     <t>Atualizar do status do processo</t>
   </si>
   <si>
+    <t>5312703512</t>
+  </si>
+  <si>
     <t>Testar compras SPOT</t>
   </si>
   <si>
-    <t>22847</t>
+    <t>05/11/2023</t>
+  </si>
+  <si>
+    <t>5367331370</t>
   </si>
   <si>
     <t>Web service para movimentação</t>
   </si>
   <si>
-    <t>21214</t>
+    <t>06/11/2023</t>
+  </si>
+  <si>
+    <t>5367355150</t>
   </si>
   <si>
     <t>Sistema de relatório e PDI's</t>
@@ -288,25 +327,19 @@
     <t>Análise de aderência Sistema de Engenharia</t>
   </si>
   <si>
-    <t>22/10/2023</t>
-  </si>
-  <si>
-    <t>22695</t>
+    <t>5366125867</t>
   </si>
   <si>
     <t>Dashboard sistema da desmoldagem</t>
   </si>
   <si>
-    <t>22764</t>
+    <t>5384625917</t>
   </si>
   <si>
     <t>Visualização da Etiqueta</t>
   </si>
   <si>
-    <t>24/10/2023</t>
-  </si>
-  <si>
-    <t>22949</t>
+    <t>5405841531</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Modelos Revenda - Alexandre Longo</t>
@@ -315,13 +348,13 @@
     <t>27/10/2023</t>
   </si>
   <si>
-    <t>22948</t>
+    <t>5405843140</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Itens Comerciais - Alexandre Longo</t>
   </si>
   <si>
-    <t>14939</t>
+    <t>5470301689</t>
   </si>
   <si>
     <t>Opção para exportar funil de projeto para excel</t>
@@ -330,6 +363,9 @@
     <t>07/11/2023</t>
   </si>
   <si>
+    <t>5290977030</t>
+  </si>
+  <si>
     <t>Homologação PDI Eletrônico</t>
   </si>
   <si>
@@ -354,6 +390,9 @@
     <t>5377369052</t>
   </si>
   <si>
+    <t>5384634175</t>
+  </si>
+  <si>
     <t>Layout da Etiqueta</t>
   </si>
   <si>
@@ -363,7 +402,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-22</t>
+    <t>Dez/2022</t>
   </si>
   <si>
     <t>Base</t>
@@ -427,6 +466,9 @@
   </si>
   <si>
     <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Fazendo</t>
@@ -1052,7 +1094,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1069,25 +1111,25 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1096,7 +1138,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1108,7 +1150,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>35</v>
@@ -1116,7 +1158,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1128,10 +1170,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>32</v>
@@ -1146,7 +1188,7 @@
         <v>33</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1163,7 +1205,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1175,13 +1217,13 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
@@ -1193,7 +1235,7 @@
         <v>33</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1210,7 +1252,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1222,10 +1264,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>32</v>
@@ -1240,7 +1282,7 @@
         <v>33</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1257,7 +1299,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1269,10 +1311,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>32</v>
@@ -1304,7 +1346,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1316,10 +1358,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>32</v>
@@ -1334,7 +1376,7 @@
         <v>33</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1351,7 +1393,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1363,10 +1405,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>32</v>
@@ -1381,7 +1423,7 @@
         <v>33</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1398,7 +1440,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1410,10 +1452,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>32</v>
@@ -1428,7 +1470,7 @@
         <v>33</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1445,7 +1487,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1457,10 +1499,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
@@ -1475,7 +1517,7 @@
         <v>33</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1492,7 +1534,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1504,10 +1546,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -1522,7 +1564,7 @@
         <v>33</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1539,7 +1581,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1551,13 +1593,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1566,10 +1608,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1578,15 +1620,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1598,14 +1640,14 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
       </c>
@@ -1613,10 +1655,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1625,30 +1667,30 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>32</v>
@@ -1660,10 +1702,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1672,30 +1714,30 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>32</v>
@@ -1707,10 +1749,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1719,7 +1761,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>35</v>
@@ -1727,22 +1769,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>32</v>
@@ -1754,10 +1796,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1766,7 +1808,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>35</v>
@@ -1774,22 +1816,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>32</v>
@@ -1801,10 +1843,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1813,7 +1855,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>35</v>
@@ -1821,25 +1863,25 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1848,10 +1890,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1860,7 +1902,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>35</v>
@@ -1868,25 +1910,25 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>21</v>
@@ -1895,10 +1937,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1907,7 +1949,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>35</v>
@@ -1915,25 +1957,25 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -1942,10 +1984,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1954,7 +1996,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>35</v>
@@ -1962,22 +2004,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>32</v>
@@ -1992,7 +2034,7 @@
         <v>33</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2009,22 +2051,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>32</v>
@@ -2039,7 +2081,7 @@
         <v>33</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2056,25 +2098,25 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2083,10 +2125,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2103,7 +2145,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2115,10 +2157,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2133,7 +2175,7 @@
         <v>33</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2150,7 +2192,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2162,10 +2204,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -2177,10 +2219,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2197,7 +2239,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2209,10 +2251,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -2224,10 +2266,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2244,7 +2286,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2256,10 +2298,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
@@ -2271,10 +2313,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2291,7 +2333,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2303,10 +2345,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -2318,10 +2360,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2330,30 +2372,30 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>32</v>
@@ -2365,10 +2407,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2377,7 +2419,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>35</v>
@@ -2385,25 +2427,25 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2412,10 +2454,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2432,25 +2474,25 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2459,10 +2501,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2479,25 +2521,25 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2506,10 +2548,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2526,7 +2568,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2538,10 +2580,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>32</v>
@@ -2553,10 +2595,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2584,23 +2626,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2608,16 +2650,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2628,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>21.69</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2636,7 +2678,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2649,7 +2691,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2657,7 +2699,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2688,12 +2730,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B2">
         <v>35</v>
@@ -2707,7 +2749,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2717,25 +2759,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2752,13 +2794,13 @@
         <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2770,21 +2812,21 @@
         <v>35</v>
       </c>
       <c r="P10" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H11">
         <v>6</v>
@@ -2796,21 +2838,21 @@
         <v>35</v>
       </c>
       <c r="M11" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2822,25 +2864,25 @@
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="Q12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>17</v>
       </c>
@@ -2854,33 +2896,27 @@
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13">
-        <v>9</v>
-      </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="M14" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2888,7 +2924,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2896,7 +2932,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2904,7 +2940,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2912,10 +2948,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2923,7 +2959,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2931,142 +2967,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
